--- a/backend/data/excel/1a6ff8ca7437_data.xlsx
+++ b/backend/data/excel/1a6ff8ca7437_data.xlsx
@@ -617,7 +617,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2025-10-17 00:15:39</t>
+          <t>2025-10-17 08:27:19</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>다운로드 시간 : 2025-10-17   00:07</t>
+          <t>다운로드 시간 : 2025-10-17   08:20</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
